--- a/data/Condition.xlsx
+++ b/data/Condition.xlsx
@@ -473,120 +473,8 @@
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>uint32</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>uint32</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>repeated uint32</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>repeated uint32</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>repeated uint32</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>repeated uint32</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>uint64</t>
-        </is>
-      </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>uint32</t>
-        </is>
-      </c>
-      <c r="R2" t="inlineStr">
-        <is>
-          <t>uint32</t>
-        </is>
-      </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>uint32</t>
-        </is>
-      </c>
-      <c r="T2" t="inlineStr">
-        <is>
-          <t>int32</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>common</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>common</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>common</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>common</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>common</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>common</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>common</t>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>common</t>
-        </is>
-      </c>
-      <c r="R3" t="inlineStr">
-        <is>
-          <t>common</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>common</t>
-        </is>
-      </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>designer</t>
-        </is>
-      </c>
-    </row>
+    <row r="2"/>
+    <row r="3"/>
     <row r="4"/>
     <row r="5">
       <c r="B5" t="inlineStr">
